--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486284_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486284_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7795</v>
+        <v>5.4888</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5759</v>
+        <v>5.1482</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2036</v>
+        <v>0.3406</v>
       </c>
       <c r="G2" t="n">
         <v>1.2138</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5657</v>
+        <v>1.275</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1823</v>
+        <v>0.7547</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3834</v>
+        <v>0.5203</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0774</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.526</v>
+        <v>1.9055</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5514</v>
+        <v>-1.2044</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.0648</v>
+        <v>0.1644</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4623</v>
+        <v>-2.5154</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6025</v>
+        <v>2.6798</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.133</v>
+        <v>1.8141</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2806</v>
+        <v>-0.6721</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4136</v>
+        <v>2.4862</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9318</v>
+        <v>-1.6497</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7429</v>
+        <v>-1.8433</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1889</v>
+        <v>0.1936</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2743</v>
+        <v>0.2316</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7487</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5256</v>
+        <v>0.1403</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0854</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2173</v>
+        <v>0.4707</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1412</v>
+        <v>0.1042</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3585</v>
+        <v>0.3665</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1644</v>
+        <v>-2.0648</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.5154</v>
+        <v>-0.4623</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6798</v>
+        <v>-1.6025</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8141</v>
+        <v>-0.133</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6721</v>
+        <v>1.2806</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4862</v>
+        <v>-1.4136</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6497</v>
+        <v>-1.9318</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8433</v>
+        <v>-1.7429</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1936</v>
+        <v>-0.1889</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
+        <v>-2.1751</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.9576</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6675</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.0854</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.0854</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.6868</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.6729000000000001</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.0138</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.5649999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2569</v>
+        <v>0.2877</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5645</v>
+        <v>-0.359</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3076</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>-2.4675</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5719</v>
+        <v>-0.0273</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2019</v>
+        <v>0.0036</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.37</v>
+        <v>-0.031</v>
       </c>
       <c r="V5" t="n">
         <v>1.695</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.3027</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0453</v>
+        <v>-1.4878</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7717000000000001</v>
+        <v>1.1851</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8495</v>
+        <v>-0.8706</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.8345</v>
+        <v>-0.8244</v>
       </c>
       <c r="I6" t="n">
-        <v>1.985</v>
+        <v>-0.0462</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1706</v>
+        <v>-0.2489</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3227</v>
+        <v>0.438</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4933</v>
+        <v>-0.6869</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0202</v>
+        <v>-0.6217</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5118</v>
+        <v>-1.2624</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4916</v>
+        <v>0.6407</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2708</v>
+        <v>0.0454</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8292</v>
+        <v>-0.1514</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5584</v>
+        <v>0.1968</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0207</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1507</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0863</v>
+        <v>-0.8381</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3639</v>
+        <v>-0.4671</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2776</v>
+        <v>-0.371</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8706</v>
+        <v>-0.8495</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8244</v>
+        <v>-2.8345</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0462</v>
+        <v>1.985</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2489</v>
+        <v>0.1706</v>
       </c>
       <c r="K7" t="n">
-        <v>0.438</v>
+        <v>-1.3227</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6869</v>
+        <v>1.4933</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6217</v>
+        <v>-1.0202</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2624</v>
+        <v>-1.5118</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6407</v>
+        <v>0.4916</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7382</v>
+        <v>0.2497</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0274</v>
+        <v>0.4074</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2892</v>
+        <v>-0.1577</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.0207</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.1507</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.39</v>
+        <v>-2.1961</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1818</v>
+        <v>-1.8646</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2082</v>
+        <v>-0.3315</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5476</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3528</v>
+        <v>0.5468</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0649</v>
+        <v>0.2524</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4177</v>
+        <v>0.2944</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1952</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. PENO</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.786</v>
+        <v>-2.3147</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5376</v>
+        <v>-2.6017</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2484</v>
+        <v>0.287</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5389</v>
+        <v>1.2475</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2075</v>
+        <v>-2.9559</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6686</v>
+        <v>4.2034</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0201</v>
+        <v>2.6526</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7086</v>
+        <v>-1.0791</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6885</v>
+        <v>3.7317</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5188</v>
+        <v>-1.4051</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4989</v>
+        <v>-1.8768</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0199</v>
+        <v>0.4717</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5225</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>-4.3501</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>2.3926</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7245</v>
+        <v>-0.3001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>-0.1646</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.382</v>
+        <v>-0.1355</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.3045</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>S. PENO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6278</v>
+        <v>-2.5316</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4525</v>
+        <v>-2.3141</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1754</v>
+        <v>-0.2175</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2475</v>
+        <v>-0.5389</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9559</v>
+        <v>-1.2075</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2034</v>
+        <v>0.6686</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6526</v>
+        <v>-0.0201</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0791</v>
+        <v>-0.7086</v>
       </c>
       <c r="L10" t="n">
-        <v>3.7317</v>
+        <v>0.6885</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4051</v>
+        <v>-0.5188</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8768</v>
+        <v>-0.4989</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4717</v>
+        <v>-0.0199</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9576</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6133</v>
+        <v>-0.4702</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0154</v>
+        <v>-0.119</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5979</v>
+        <v>-0.3512</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3045</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.413</v>
+        <v>-6.1325</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.476</v>
+        <v>-5.0722</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9371</v>
+        <v>-1.0603</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3917</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3237</v>
+        <v>-0.0433</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.399</v>
+        <v>0.0048</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0752</v>
+        <v>-0.0481</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.737400000000001</v>
+        <v>-7.3674</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.378500000000001</v>
+        <v>-7.0086</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3591000000000001</v>
+        <v>-0.3587999999999998</v>
       </c>
       <c r="G12" t="n">
         <v>-9.104899999999999</v>
@@ -1366,10 +1366,10 @@
         <v>3.2521</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.6967</v>
+        <v>-4.696700000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9489</v>
+        <v>7.948900000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-12.3571</v>
@@ -1390,10 +1390,10 @@
         <v>15.2255</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8051999999999996</v>
+        <v>2.1751</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03619999999999979</v>
+        <v>1.4061</v>
       </c>
       <c r="U12" t="n">
         <v>0.7689999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.5488</v>
+        <v>8.315099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5118</v>
+        <v>6.2883</v>
       </c>
       <c r="F13" t="n">
-        <v>2.037</v>
+        <v>2.0268</v>
       </c>
       <c r="G13" t="n">
         <v>5.3996</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6044</v>
+        <v>0.3707</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0649</v>
+        <v>-0.2884</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6693</v>
+        <v>0.6591</v>
       </c>
       <c r="V13" t="n">
         <v>0.3698</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2434</v>
+        <v>3.657</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7305</v>
+        <v>1.507</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5129</v>
+        <v>2.15</v>
       </c>
       <c r="G14" t="n">
         <v>2.1679</v>
@@ -1546,13 +1546,13 @@
         <v>2.6101</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8375</v>
+        <v>-0.4239</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2704</v>
+        <v>-0.4939</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5671</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.3904</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. FILIPOVIC</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5483</v>
+        <v>2.5799</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1172</v>
+        <v>0.0696</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4311</v>
+        <v>2.5104</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1885</v>
+        <v>2.4297</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0737</v>
+        <v>2.1317</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1148</v>
+        <v>0.298</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3089</v>
+        <v>2.9933</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0251</v>
+        <v>1.4234</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2838</v>
+        <v>1.5698</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1204</v>
+        <v>-0.5636</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0486</v>
+        <v>0.7083</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1689</v>
+        <v>-1.2718</v>
       </c>
       <c r="P15" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-2.1751</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.6101</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.2848</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.7486</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="V15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.0875</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.0875</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.7295</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.2656</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.3698</v>
-      </c>
       <c r="W15" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>G. FILIPOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1932</v>
+        <v>2.3827</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2657</v>
+        <v>1.2289</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4589</v>
+        <v>1.1537</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4297</v>
+        <v>2.1885</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1317</v>
+        <v>1.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>0.298</v>
+        <v>1.1148</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9933</v>
+        <v>2.3089</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4234</v>
+        <v>1.0251</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5698</v>
+        <v>1.2838</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5636</v>
+        <v>-0.1204</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7083</v>
+        <v>0.0486</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2718</v>
+        <v>-0.1689</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6101</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6715</v>
+        <v>0.5639</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0839</v>
+        <v>0.3773</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4124</v>
+        <v>0.1866</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1587</v>
+        <v>1.5177</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2979</v>
+        <v>-0.7079</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8608</v>
+        <v>2.2256</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1926</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>1.372</v>
+        <v>0.7309</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7557</v>
+        <v>0.7499</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3837</v>
+        <v>-0.0189</v>
       </c>
       <c r="V17" t="n">
         <v>0.5443</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.756</v>
+        <v>0.2722</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2437</v>
+        <v>0.2281</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5123</v>
+        <v>0.0442</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3965</v>
+        <v>-0.0556</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.006</v>
+        <v>1.77</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3905</v>
+        <v>-1.8256</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0116</v>
+        <v>0.4745</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0881</v>
+        <v>1.0283</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0765</v>
+        <v>-0.5538</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3849</v>
+        <v>-0.5301</v>
       </c>
       <c r="N18" t="n">
-        <v>0.082</v>
+        <v>0.7417</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.467</v>
+        <v>-1.2718</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6525</v>
+        <v>2.8276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.435</v>
+        <v>2.8276</v>
       </c>
       <c r="S18" t="n">
-        <v>1.24</v>
+        <v>-0.6303</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1476</v>
+        <v>-0.6369</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0924</v>
+        <v>0.0066</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.8695</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>0.3904</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3698</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5088</v>
+        <v>0.1664</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.219</v>
+        <v>-0.3151</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2898</v>
+        <v>0.4814</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0556</v>
+        <v>-0.3965</v>
       </c>
       <c r="H19" t="n">
-        <v>1.77</v>
+        <v>-0.006</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8256</v>
+        <v>-0.3905</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4745</v>
+        <v>-0.0116</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0283</v>
+        <v>-0.0881</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5538</v>
+        <v>0.0765</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5301</v>
+        <v>-0.3849</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7417</v>
+        <v>0.082</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2718</v>
+        <v>-0.467</v>
       </c>
       <c r="P19" t="n">
-        <v>2.8276</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8276</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4113</v>
+        <v>0.6504</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0839</v>
+        <v>0.5888</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3274</v>
+        <v>0.0616</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8695</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3904</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2599</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8728</v>
+        <v>-1.4065</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9202</v>
+        <v>-1.3614</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0474</v>
+        <v>-0.0451</v>
       </c>
       <c r="G20" t="n">
         <v>0.7632</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3957</v>
+        <v>0.0706</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3577</v>
+        <v>0.2653</v>
       </c>
       <c r="V20" t="n">
         <v>0.3698</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0375</v>
+        <v>-2.8513</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5888</v>
+        <v>-2.7006</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4487</v>
+        <v>-0.1507</v>
       </c>
       <c r="G21" t="n">
         <v>-0.385</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2175</v>
+        <v>-0.0312</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0036</v>
+        <v>-0.1081</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2211</v>
+        <v>0.0769</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2919</v>
+        <v>-4.4056</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5485</v>
+        <v>-3.8779</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7435</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8143</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2177</v>
+        <v>-0.3314</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.0144</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5327</v>
+        <v>-0.317</v>
       </c>
       <c r="V22" t="n">
         <v>-1.695</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8.737400000000001</v>
+        <v>10.2276</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3589000000000002</v>
+        <v>0.3590000000000004</v>
       </c>
       <c r="F23" t="n">
-        <v>8.378399999999999</v>
+        <v>9.868600000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>9.104900000000002</v>
+        <v>9.104900000000001</v>
       </c>
       <c r="H23" t="n">
         <v>18.5675</v>
@@ -2248,13 +2248,13 @@
         <v>18.4881</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8052999999999998</v>
+        <v>0.6849000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7691000000000003</v>
+        <v>-0.7689999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0361999999999999</v>
+        <v>1.454</v>
       </c>
       <c r="V23" t="n">
         <v>-2.825</v>
